--- a/data/trans_bre/P19C01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 8,48</t>
+          <t>-2,19; 8,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,56; 15,91</t>
+          <t>5,05; 15,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 10,49</t>
+          <t>-0,9; 10,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 7,51</t>
+          <t>-3,5; 6,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 43,01</t>
+          <t>-8,21; 43,77</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,9; 83,22</t>
+          <t>20,07; 80,06</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 33,3</t>
+          <t>-2,49; 34,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 15,96</t>
+          <t>-6,33; 14,46</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 7,47</t>
+          <t>-1,75; 8,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 8,04</t>
+          <t>-1,06; 7,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 5,79</t>
+          <t>-4,5; 5,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,23; 35,81</t>
+          <t>0,13; 37,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 27,91</t>
+          <t>-5,62; 29,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 29,8</t>
+          <t>-3,22; 29,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,49; 15,85</t>
+          <t>-10,68; 13,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,33; 143,12</t>
+          <t>0,32; 155,38</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 4,54</t>
+          <t>-6,26; 4,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,78; 5,91</t>
+          <t>-5,12; 5,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 9,8</t>
+          <t>-1,65; 10,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-35,93; -0,08</t>
+          <t>-34,13; -0,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-18,66; 17,94</t>
+          <t>-19,97; 16,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 20,55</t>
+          <t>-14,45; 19,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 27,61</t>
+          <t>-3,82; 29,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -0,3</t>
+          <t>-62,39; -0,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 5,73</t>
+          <t>-4,24; 5,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 9,58</t>
+          <t>0,22; 10,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 6,8</t>
+          <t>-3,07; 7,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 11,28</t>
+          <t>-0,72; 11,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,52; 17,75</t>
+          <t>-10,93; 17,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 31,62</t>
+          <t>0,64; 34,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,89; 15,74</t>
+          <t>-6,57; 16,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 19,06</t>
+          <t>-1,29; 18,34</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,38</t>
+          <t>-0,92; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,35</t>
+          <t>2,26; 7,21</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>-0,07; 5,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 13,4</t>
+          <t>-6,45; 12,36</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 15,35</t>
+          <t>-2,99; 14,75</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 25,47</t>
+          <t>7,3; 25,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,58</t>
+          <t>-0,16; 13,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 29,22</t>
+          <t>-11,11; 26,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,84</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 8,44</t>
+          <t>-2,58; 8,42</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,05; 15,55</t>
+          <t>5,65; 15,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 10,93</t>
+          <t>-1,34; 10,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 6,82</t>
+          <t>-2,69; 7,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 43,77</t>
+          <t>-10,39; 40,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,07; 80,06</t>
+          <t>22,89; 79,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 34,03</t>
+          <t>-3,71; 33,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 14,46</t>
+          <t>-5,0; 15,98</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14,2</t>
+          <t>2,31</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 8,07</t>
+          <t>-2,34; 7,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 7,99</t>
+          <t>-1,24; 8,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 5,1</t>
+          <t>-4,36; 5,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 37,94</t>
+          <t>-2,23; 6,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 29,4</t>
+          <t>-7,15; 27,25</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 29,2</t>
+          <t>-3,53; 30,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 13,32</t>
+          <t>-9,81; 13,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 155,38</t>
+          <t>-3,41; 11,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-14,17</t>
+          <t>0,81</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-25,93%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 4,14</t>
+          <t>-5,84; 5,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 5,68</t>
+          <t>-4,63; 6,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 10,26</t>
+          <t>-2,4; 9,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-34,13; -0,41</t>
+          <t>-4,6; 5,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-19,97; 16,43</t>
+          <t>-18,57; 20,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,45; 19,66</t>
+          <t>-13,49; 21,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 29,31</t>
+          <t>-6,16; 25,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-62,39; -0,97</t>
+          <t>-8,22; 11,61</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,82</t>
+          <t>2,2</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 5,91</t>
+          <t>-3,72; 5,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 10,23</t>
+          <t>0,3; 9,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 7,08</t>
+          <t>-2,67; 7,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 11,0</t>
+          <t>-2,29; 6,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 17,99</t>
+          <t>-9,84; 17,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 34,4</t>
+          <t>0,84; 31,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 16,28</t>
+          <t>-5,47; 16,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 18,34</t>
+          <t>-3,62; 10,49</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,24</t>
+          <t>-0,99; 4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,21</t>
+          <t>2,25; 7,22</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,15</t>
+          <t>-0,41; 5,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 12,36</t>
+          <t>-0,4; 4,49</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 14,75</t>
+          <t>-3,12; 15,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,3; 25,27</t>
+          <t>7,37; 25,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 13,16</t>
+          <t>-0,96; 13,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 26,99</t>
+          <t>-0,66; 8,03</t>
         </is>
       </c>
     </row>
